--- a/ხელფასები ცელერისი.xlsx
+++ b/ხელფასები ცელერისი.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\deliverer\დეკლარაცია\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3945F6EE-A92D-4DCF-AFA0-B25A68832C8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE26D2F6-3128-4C49-B577-D985F19D5ECD}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ხელფასები" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ხელფასები!$H$7:$J$13</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="65">
   <si>
     <t>თარიღი</t>
   </si>
@@ -724,26 +724,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S73"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="8.88671875" style="11"/>
-    <col min="3" max="3" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="11"/>
-    <col min="8" max="8" width="9.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="18" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" style="18" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" style="11" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" customWidth="1"/>
-    <col min="15" max="15" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" style="11" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" style="11"/>
-    <col min="18" max="19" width="10.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="2" width="8.90625" style="11"/>
+    <col min="3" max="3" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="11"/>
+    <col min="8" max="8" width="9.54296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" style="18" customWidth="1"/>
+    <col min="11" max="11" width="10.36328125" customWidth="1"/>
+    <col min="12" max="12" width="10.36328125" style="18" customWidth="1"/>
+    <col min="13" max="13" width="10.36328125" style="11" customWidth="1"/>
+    <col min="14" max="14" width="10.36328125" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.90625" style="11" customWidth="1"/>
+    <col min="17" max="17" width="8.90625" style="11"/>
+    <col min="18" max="19" width="10.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="8.90625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -770,7 +770,7 @@
     </row>
     <row r="2" spans="1:17">
       <c r="C2" s="31">
-        <v>46118</v>
+        <v>46146</v>
       </c>
       <c r="D2" t="s">
         <v>63</v>
@@ -780,6 +780,10 @@
       </c>
       <c r="F2" s="28">
         <v>300</v>
+      </c>
+      <c r="G2" s="11">
+        <f>F2/0.8/0.98</f>
+        <v>382.65306122448982</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -791,7 +795,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="C3" s="31">
-        <v>46126</v>
+        <v>46153</v>
       </c>
       <c r="D3" t="s">
         <v>63</v>
@@ -801,6 +805,10 @@
       </c>
       <c r="F3" s="28">
         <v>300</v>
+      </c>
+      <c r="G3" s="11">
+        <f t="shared" ref="G3:G5" si="0">F3/0.8/0.98</f>
+        <v>382.65306122448982</v>
       </c>
       <c r="I3" s="25"/>
       <c r="J3" s="25"/>
@@ -813,7 +821,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="C4" s="31">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D4" t="s">
         <v>63</v>
@@ -822,7 +830,11 @@
         <v>62</v>
       </c>
       <c r="F4" s="28">
-        <v>500</v>
+        <v>300</v>
+      </c>
+      <c r="G4" s="11">
+        <f t="shared" si="0"/>
+        <v>382.65306122448982</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
@@ -834,10 +846,22 @@
       <c r="Q4" s="15"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="C5" s="31"/>
-      <c r="D5"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="28"/>
+      <c r="C5" s="31">
+        <v>46167</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="28">
+        <v>100</v>
+      </c>
+      <c r="G5" s="11">
+        <f t="shared" si="0"/>
+        <v>127.55102040816327</v>
+      </c>
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="15"/>
@@ -1425,9 +1449,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2165,10 +2189,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P69"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" customWidth="1"/>
+    <col min="4" max="4" width="24.90625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2262,7 +2286,7 @@
       </c>
       <c r="K2" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C2))&gt;1,DAY(ხელფასები!C2),CONCATENATE("0",DAY(ხელფასები!C2))),"/",MONTH(ხელფასები!C2),"/",YEAR(ხელფასები!C2))</f>
-        <v>06/4/2026</v>
+        <v>04/5/2026</v>
       </c>
       <c r="L2" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D2,ხელფასები!E2),map!$A$1:$P$102,12,FALSE)</f>
@@ -2327,7 +2351,7 @@
       </c>
       <c r="K3" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C3))&gt;1,DAY(ხელფასები!C3),CONCATENATE("0",DAY(ხელფასები!C3))),"/",MONTH(ხელფასები!C3),"/",YEAR(ხელფასები!C3))</f>
-        <v>14/4/2026</v>
+        <v>11/5/2026</v>
       </c>
       <c r="L3" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D3,ხელფასები!E3),map!$A$1:$P$102,12,FALSE)</f>
@@ -2381,18 +2405,18 @@
       </c>
       <c r="H4">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F4/0.8,ხელფასები!F4/0.8/0.98)</f>
-        <v>637.75510204081638</v>
+        <v>382.65306122448982</v>
       </c>
       <c r="I4" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F4/0.8/0.98*0.02)</f>
-        <v>12.755102040816327</v>
+        <v>7.6530612244897966</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C4))&gt;1,DAY(ხელფასები!C4),CONCATENATE("0",DAY(ხელფასები!C4))),"/",MONTH(ხელფასები!C4),"/",YEAR(ხელფასები!C4))</f>
-        <v>27/4/2026</v>
+        <v>18/5/2026</v>
       </c>
       <c r="L4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,12,FALSE)</f>
@@ -2400,7 +2424,7 @@
       </c>
       <c r="M4">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F4/0.8*0.2,(ხელფასები!F4/0.8/0.98-ხელფასები!F4/0.8/0.98*0.02)*0.2)</f>
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="N4" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D4,ხელფასები!E4),map!$A$1:$P$102,14,FALSE)</f>
@@ -2416,66 +2440,66 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5">
+      <c r="A5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$100,2,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="B5">
+        <v>01911104191</v>
+      </c>
+      <c r="B5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$120,3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C5">
+        <v>მარიამი</v>
+      </c>
+      <c r="C5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$120,4,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D5">
+        <v>გულბანი</v>
+      </c>
+      <c r="D5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,5,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="E5">
+        <v>თბილისი</v>
+      </c>
+      <c r="E5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,6,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F5">
+        <v>268</v>
+      </c>
+      <c r="F5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,7,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,8,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F5/0.8,ხელფასები!F5/0.8/0.98)</f>
-        <v>0</v>
+        <v>127.55102040816327</v>
       </c>
       <c r="I5" s="5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,10,FALSE)="0","0",ხელფასები!F5/0.8/0.98*0.02)</f>
-        <v>0</v>
+        <v>2.5510204081632653</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="str">
         <f>CONCATENATE(IF(LEN(DAY(ხელფასები!C5))&gt;1,DAY(ხელფასები!C5),CONCATENATE("0",DAY(ხელფასები!C5))),"/",MONTH(ხელფასები!C5),"/",YEAR(ხელფასები!C5))</f>
-        <v>00/1/1900</v>
-      </c>
-      <c r="L5">
+        <v>25/5/2026</v>
+      </c>
+      <c r="L5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,12,FALSE)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M5">
         <f>IF(VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,10,FALSE)="0",ხელფასები!F5/0.8*0.2,(ხელფასები!F5/0.8/0.98-ხელფასები!F5/0.8/0.98*0.02)*0.2)</f>
-        <v>0</v>
-      </c>
-      <c r="N5">
+        <v>25</v>
+      </c>
+      <c r="N5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,14,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,15,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="str">
         <f>VLOOKUP(CONCATENATE(ხელფასები!D5,ხელფასები!E5),map!$A$1:$P$102,16,FALSE)</f>
         <v>0</v>
       </c>
@@ -6648,7 +6672,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -6688,7 +6712,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
@@ -6796,11 +6820,11 @@
       </c>
       <c r="D5">
         <f>SUMIF('გადასატანი ცხრილი'!$A$1:$A$205,'უნიკალური პ.ნ.'!A6,'გადასატანი ცხრილი'!$H$1:$H$205)</f>
-        <v>1403.0612244897961</v>
+        <v>1275.5102040816328</v>
       </c>
       <c r="E5">
         <f>SUMIF('გადასატანი ცხრილი'!$A$1:$A$205,'უნიკალური პ.ნ.'!A6,'გადასატანი ცხრილი'!$I$1:$I$205)*2</f>
-        <v>56.122448979591837</v>
+        <v>51.020408163265309</v>
       </c>
     </row>
     <row r="6" spans="1:5">
